--- a/assets/tds/Tableau Competences Nawiss.xlsx
+++ b/assets/tds/Tableau Competences Nawiss.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lloyd\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lloyd\Documents\Ecole\portfolio nawiss\assets\tds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E97336E-4BCB-41CA-9D24-6C54D39E43E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AADB90-1103-4152-A78C-6EA4B379B5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,12 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="54">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
-  </si>
-  <si>
-    <t>SESSION 2024</t>
   </si>
   <si>
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
@@ -129,9 +126,6 @@
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t xml:space="preserve">Adresse URL du portfolio : </t>
-  </si>
-  <si>
     <t>Tp Jeux de dés Java</t>
   </si>
   <si>
@@ -139,9 +133,6 @@
   </si>
   <si>
     <t>Tp RPG Sim en groupe Java</t>
-  </si>
-  <si>
-    <t>NOM et prénom : Nawiss Makaya</t>
   </si>
   <si>
     <t>Centre de formation : Campus du Beaujolais by csnd, Villefranche/Saone</t>
@@ -173,6 +164,83 @@
   <si>
     <t>Transport School (Projet en trio)</t>
   </si>
+  <si>
+    <t>SESSION 2026</t>
+  </si>
+  <si>
+    <t>05/01/26 au 13/02/26</t>
+  </si>
+  <si>
+    <t>Création de site web chez Baanne Biisse</t>
+  </si>
+  <si>
+    <t>Réalisation en cours de formation</t>
+  </si>
+  <si>
+    <t>Site pour complement alimentaire (personnel)</t>
+  </si>
+  <si>
+    <t>site de vente d'art (personnel)</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://nawiss8.github.io/Portfolio/index.html</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  x</t>
+    </r>
+  </si>
+  <si>
+    <t>application pour la music (pour les epreuves : en developpement)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">             </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> x</t>
+    </r>
+  </si>
+  <si>
+    <t>11/02/2026 et +</t>
+  </si>
+  <si>
+    <t>25/03/2026 au 20/04/26</t>
+  </si>
+  <si>
+    <t>10/11/25 au 27/03/26</t>
+  </si>
+  <si>
+    <t>24/03/26 au 05/05/26</t>
+  </si>
+  <si>
+    <t>NOM et prénom : Nawiss Makaya Tchicaya</t>
+  </si>
+  <si>
+    <t>Aplication de rencontre : Muggu (pour epreuves : abandon)</t>
+  </si>
+  <si>
+    <t>Site de voiture v1  (pour epreuves : terminé)</t>
+  </si>
+  <si>
+    <t>Site de voiture v2  (pour epreuves : terminé)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veille technologique : IA </t>
+  </si>
 </sst>
 </file>
 
@@ -181,7 +249,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -235,6 +303,11 @@
     <font>
       <b/>
       <sz val="20"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -649,12 +722,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -705,6 +772,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -788,6 +859,7188 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>360</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BACB26C-8926-94B2-68EB-9D2EEEB9DA8C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7967160" y="16584438"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BACB26C-8926-94B2-68EB-9D2EEEB9DA8C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7961040" y="16578318"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>5040</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>360</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="3" name="Ink 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1525EA11-2733-F5F8-FC94-F5EE502D1681}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7615440" y="16562118"/>
+            <a:ext cx="5040" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="3" name="Ink 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1525EA11-2733-F5F8-FC94-F5EE502D1681}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7609320" y="16555998"/>
+              <a:ext cx="17280" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>180795</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>323775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>181155</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>324135</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="11" name="Ink 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{450CAC6B-21B2-4C15-0EC9-82A3E6A0E0BE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5600520" y="2352600"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="11" name="Ink 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{450CAC6B-21B2-4C15-0EC9-82A3E6A0E0BE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5594400" y="2346480"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>542505</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>477960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>542865</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>495600</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="12" name="Ink 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C2C40F3-2DBF-18A1-C228-0CFA68DE3AEF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="13448880" y="2001960"/>
+            <a:ext cx="360" cy="17640"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="12" name="Ink 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C2C40F3-2DBF-18A1-C228-0CFA68DE3AEF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13442760" y="1995840"/>
+              <a:ext cx="12600" cy="29880"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>790275</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>209505</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>790635</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>209865</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="13" name="Ink 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{921B9933-1F6E-A2CE-794D-C5BC18365CFD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="6210000" y="1228680"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="13" name="Ink 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{921B9933-1F6E-A2CE-794D-C5BC18365CFD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6203880" y="1222560"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>933150</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>323625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>933510</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>323985</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="14" name="Ink 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7308B1A-EA56-9B12-7934-477C042531A6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10096200" y="1342800"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="14" name="Ink 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7308B1A-EA56-9B12-7934-477C042531A6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10090080" y="1336680"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1076070</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>371145</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>104415</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>457185</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="15" name="Ink 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B89E29B-EA70-5A0C-8BEF-E46D317CBE1D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="10239120" y="1390320"/>
+            <a:ext cx="276120" cy="86040"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="15" name="Ink 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B89E29B-EA70-5A0C-8BEF-E46D317CBE1D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10233000" y="1384200"/>
+              <a:ext cx="288360" cy="98280"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2295720</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>19320</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="16" name="Ink 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{791ECB02-E794-47E4-EED5-987AF1B6BBF3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="16" name="Ink 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{791ECB02-E794-47E4-EED5-987AF1B6BBF3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="18" name="Ink 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F726EB3D-4DB6-4BD9-A3EF-98D4B7EB8A02}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="18" name="Ink 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F726EB3D-4DB6-4BD9-A3EF-98D4B7EB8A02}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="19" name="Ink 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8390234-B437-48C8-BF96-3042BEF3EFB2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="19" name="Ink 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8390234-B437-48C8-BF96-3042BEF3EFB2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="20" name="Ink 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFDCF722-B5F0-4EF6-85D2-B389794E40B3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="20" name="Ink 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFDCF722-B5F0-4EF6-85D2-B389794E40B3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="21" name="Ink 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{213F095B-4717-4DA5-82C7-7A20CD493FE8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="21" name="Ink 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{213F095B-4717-4DA5-82C7-7A20CD493FE8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="22" name="Ink 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E9D3736-AE48-492B-85F1-DB74264A8996}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="22" name="Ink 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E9D3736-AE48-492B-85F1-DB74264A8996}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="23" name="Ink 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E4545A6-97C2-449C-B7E0-BC770BC4CD4B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="23" name="Ink 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E4545A6-97C2-449C-B7E0-BC770BC4CD4B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="24" name="Ink 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15007A1D-F32E-4F30-8315-33CF00757931}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="24" name="Ink 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15007A1D-F32E-4F30-8315-33CF00757931}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="25" name="Ink 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D1D2806-CD44-4CBD-AE56-B7C13B37FB44}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="25" name="Ink 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D1D2806-CD44-4CBD-AE56-B7C13B37FB44}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="26" name="Ink 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CF2371C-969D-4C72-AE24-155499CC266A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="26" name="Ink 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CF2371C-969D-4C72-AE24-155499CC266A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="27" name="Ink 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3893162B-705B-414B-AED0-F432CF332919}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="27" name="Ink 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3893162B-705B-414B-AED0-F432CF332919}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="28" name="Ink 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CDFB7D6-8347-4DC3-9DC4-FDC8C3DF5047}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="28" name="Ink 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CDFB7D6-8347-4DC3-9DC4-FDC8C3DF5047}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="29" name="Ink 28">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A1F3CBA-BC52-4DFC-86F6-8C02EFCB1535}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="29" name="Ink 28">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A1F3CBA-BC52-4DFC-86F6-8C02EFCB1535}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="30" name="Ink 29">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BE20F60-1BB0-4675-A91E-B3B172D9E9AF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="30" name="Ink 29">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BE20F60-1BB0-4675-A91E-B3B172D9E9AF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="31" name="Ink 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23EAFE14-3B64-4B55-833F-9CF1C436786D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="31" name="Ink 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23EAFE14-3B64-4B55-833F-9CF1C436786D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="32" name="Ink 31">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4C98D76-59BF-469C-BBEA-9167866ECC6A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="32" name="Ink 31">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4C98D76-59BF-469C-BBEA-9167866ECC6A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="33" name="Ink 32">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78544C37-D21A-4A42-B4BB-EBBD4216C461}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="33" name="Ink 32">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78544C37-D21A-4A42-B4BB-EBBD4216C461}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId28">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="34" name="Ink 33">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA6BEF4F-D239-40F7-9290-6A00C0D73C3F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="34" name="Ink 33">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA6BEF4F-D239-40F7-9290-6A00C0D73C3F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId29">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="35" name="Ink 34">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C74D87B0-7D4F-4F74-BBF5-C7A1362D51A6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="35" name="Ink 34">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C74D87B0-7D4F-4F74-BBF5-C7A1362D51A6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId30">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="36" name="Ink 35">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F1DC075-9173-4DD3-B0C7-471068AC9E7E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="36" name="Ink 35">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F1DC075-9173-4DD3-B0C7-471068AC9E7E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId31">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="37" name="Ink 36">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACC8CB1A-D32F-4F6B-8F18-383506774AB2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="37" name="Ink 36">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACC8CB1A-D32F-4F6B-8F18-383506774AB2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId32">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="38" name="Ink 37">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E8E3ABA-EB77-4E1B-95D5-EBFCD8075B90}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="38" name="Ink 37">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E8E3ABA-EB77-4E1B-95D5-EBFCD8075B90}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId33">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="39" name="Ink 38">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DEA8386-209A-4674-8DC8-3825C565EA0F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="39" name="Ink 38">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DEA8386-209A-4674-8DC8-3825C565EA0F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId34">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="40" name="Ink 39">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CAD3567-1CC1-4E81-9F8D-56CE960F087A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="40" name="Ink 39">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CAD3567-1CC1-4E81-9F8D-56CE960F087A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId35">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="41" name="Ink 40">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5071ACB-DF59-46AB-BE8F-05005E6EB56D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="41" name="Ink 40">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5071ACB-DF59-46AB-BE8F-05005E6EB56D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId36">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="42" name="Ink 41">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CBD0454-E1E6-4E06-86D7-ACDA261FEAFA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="42" name="Ink 41">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CBD0454-E1E6-4E06-86D7-ACDA261FEAFA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId37">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="43" name="Ink 42">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{151892A2-3872-46AE-8077-A96960F65A83}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="43" name="Ink 42">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{151892A2-3872-46AE-8077-A96960F65A83}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId38">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="44" name="Ink 43">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E1FA291-C640-4445-BCED-48F5C8097734}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="44" name="Ink 43">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E1FA291-C640-4445-BCED-48F5C8097734}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId39">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="45" name="Ink 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AE72DD8-7F1A-440D-A5B0-1F1AD4E356D7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="45" name="Ink 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AE72DD8-7F1A-440D-A5B0-1F1AD4E356D7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId40">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="46" name="Ink 45">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9997172F-37FA-451F-BFB2-D36D0DB12CBB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="46" name="Ink 45">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9997172F-37FA-451F-BFB2-D36D0DB12CBB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId41">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="47" name="Ink 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C34FFBE-51C4-4D8F-A2C7-1E45E46D3B59}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="47" name="Ink 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C34FFBE-51C4-4D8F-A2C7-1E45E46D3B59}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId42">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="48" name="Ink 47">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEA996B3-D993-44A6-95FF-CF575CE08900}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="48" name="Ink 47">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEA996B3-D993-44A6-95FF-CF575CE08900}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId43">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="49" name="Ink 48">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02B060EA-9781-44B3-9A8D-F0AB61DC7BAC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="49" name="Ink 48">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02B060EA-9781-44B3-9A8D-F0AB61DC7BAC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId44">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="50" name="Ink 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C308EA65-CFB9-4349-8E4D-544B7A257D2E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="50" name="Ink 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C308EA65-CFB9-4349-8E4D-544B7A257D2E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId45">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="51" name="Ink 50">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A3D8550-390A-4FD1-8CE5-BBF4460FE5F0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="51" name="Ink 50">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A3D8550-390A-4FD1-8CE5-BBF4460FE5F0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId46">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="52" name="Ink 51">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3923043A-6236-4554-BCEC-C291BEEC9B28}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="52" name="Ink 51">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3923043A-6236-4554-BCEC-C291BEEC9B28}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId47">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="53" name="Ink 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A627FFCF-632D-4BD4-A445-6511474783B2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="53" name="Ink 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A627FFCF-632D-4BD4-A445-6511474783B2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId48">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="54" name="Ink 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E4EC479-CA30-46E2-9B03-A15D8F8F3C1A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="54" name="Ink 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E4EC479-CA30-46E2-9B03-A15D8F8F3C1A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId49">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="55" name="Ink 54">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C94B3EF8-0187-43B5-B665-1A2D265418E6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="55" name="Ink 54">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C94B3EF8-0187-43B5-B665-1A2D265418E6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId50">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="56" name="Ink 55">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C347D02-53A0-4F66-ADD9-3AE632682C2C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="56" name="Ink 55">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C347D02-53A0-4F66-ADD9-3AE632682C2C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId51">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="57" name="Ink 56">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0050153C-0AB8-4D31-A9E2-67175CF215A1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="57" name="Ink 56">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0050153C-0AB8-4D31-A9E2-67175CF215A1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId52">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="58" name="Ink 57">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AC04148-FDEA-44B8-9507-97EA44CC25CB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="58" name="Ink 57">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AC04148-FDEA-44B8-9507-97EA44CC25CB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId53">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="59" name="Ink 58">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC3EECEF-7CE8-455A-B569-5633CB445487}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="59" name="Ink 58">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC3EECEF-7CE8-455A-B569-5633CB445487}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId54">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="60" name="Ink 59">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3E1CA1C-AB0E-409D-9F7C-DF1F2DD56169}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="60" name="Ink 59">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3E1CA1C-AB0E-409D-9F7C-DF1F2DD56169}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId55">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="61" name="Ink 60">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A7535BA-363B-4EFF-A742-35C05D54A0C5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="61" name="Ink 60">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A7535BA-363B-4EFF-A742-35C05D54A0C5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId56">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="62" name="Ink 61">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4BF2730-2281-43FA-A64E-9A4526A5C5BA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="62" name="Ink 61">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4BF2730-2281-43FA-A64E-9A4526A5C5BA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId57">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="63" name="Ink 62">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F5317E9-BB98-4E5E-B333-FD8B668E6986}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="63" name="Ink 62">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F5317E9-BB98-4E5E-B333-FD8B668E6986}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId58">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="64" name="Ink 63">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8F58434-6ED9-4E6C-8204-4682BB871107}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="64" name="Ink 63">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8F58434-6ED9-4E6C-8204-4682BB871107}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId59">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="65" name="Ink 64">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CDC5F28-614B-46AF-83C6-3BB88669D223}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="65" name="Ink 64">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CDC5F28-614B-46AF-83C6-3BB88669D223}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId60">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="66" name="Ink 65">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECF0125A-22AC-43EA-B042-BD4827AB9C0C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="66" name="Ink 65">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECF0125A-22AC-43EA-B042-BD4827AB9C0C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId61">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="67" name="Ink 66">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10D69FD2-AB10-4A47-81BF-40A53126B114}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="67" name="Ink 66">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10D69FD2-AB10-4A47-81BF-40A53126B114}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId62">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="68" name="Ink 67">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7D764B7-9ADC-4B03-AD29-DC348C5FBF18}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="68" name="Ink 67">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7D764B7-9ADC-4B03-AD29-DC348C5FBF18}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId63">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="69" name="Ink 68">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE7C41D9-37D7-4EBC-86EE-EBFE47DDB76D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="69" name="Ink 68">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE7C41D9-37D7-4EBC-86EE-EBFE47DDB76D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId64">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="70" name="Ink 69">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32E6046A-83B6-4DC0-A77A-DD57BECCC6F5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="70" name="Ink 69">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32E6046A-83B6-4DC0-A77A-DD57BECCC6F5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId65">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="71" name="Ink 70">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABA02FF8-F693-47D8-84FC-FFF61A500051}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="71" name="Ink 70">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABA02FF8-F693-47D8-84FC-FFF61A500051}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId66">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="72" name="Ink 71">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F1EC051-F963-4215-9ED1-81C2387A9A84}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="72" name="Ink 71">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F1EC051-F963-4215-9ED1-81C2387A9A84}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId67">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="73" name="Ink 72">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D0C9796-1C97-448B-BAA7-857003A1A378}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="73" name="Ink 72">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D0C9796-1C97-448B-BAA7-857003A1A378}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId68">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="74" name="Ink 73">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F64D472-4CA6-4156-AC78-1D5599ED268F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="74" name="Ink 73">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F64D472-4CA6-4156-AC78-1D5599ED268F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId69">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="75" name="Ink 74">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB77B3A6-D3C3-4045-ABD5-A60236E03EC2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="75" name="Ink 74">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB77B3A6-D3C3-4045-ABD5-A60236E03EC2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId70">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="76" name="Ink 75">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7A63355-4331-4EB1-AA01-B15C2DDA5756}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="76" name="Ink 75">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7A63355-4331-4EB1-AA01-B15C2DDA5756}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId71">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="77" name="Ink 76">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB1CB744-A1FD-4A47-8AF1-2FA44591A6CB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="77" name="Ink 76">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB1CB744-A1FD-4A47-8AF1-2FA44591A6CB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId72">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="78" name="Ink 77">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D44E095-9832-4006-9658-DD031BF78376}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="78" name="Ink 77">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D44E095-9832-4006-9658-DD031BF78376}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId73">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="79" name="Ink 78">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E78F9089-B233-456A-B58D-5272B3C26C00}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="79" name="Ink 78">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E78F9089-B233-456A-B58D-5272B3C26C00}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId74">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="80" name="Ink 79">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9712E3F1-BFEC-4912-A7E9-DCDD74C63147}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="80" name="Ink 79">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9712E3F1-BFEC-4912-A7E9-DCDD74C63147}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId75">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="81" name="Ink 80">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{171E0AC8-3DCD-4933-A822-FE367601DEF4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="81" name="Ink 80">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{171E0AC8-3DCD-4933-A822-FE367601DEF4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId76">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="82" name="Ink 81">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF1431B7-367E-4277-A9F8-73547EAD481A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="82" name="Ink 81">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF1431B7-367E-4277-A9F8-73547EAD481A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId77">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="83" name="Ink 82">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91821BEC-7342-4811-92FF-C6C8D2C05537}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="83" name="Ink 82">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91821BEC-7342-4811-92FF-C6C8D2C05537}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId78">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="84" name="Ink 83">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF737EA0-2978-4FA9-BC71-F7B3767F67C2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="84" name="Ink 83">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF737EA0-2978-4FA9-BC71-F7B3767F67C2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId79">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="85" name="Ink 84">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DA2DC97-3903-4DCF-9E68-336D7F747967}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="85" name="Ink 84">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DA2DC97-3903-4DCF-9E68-336D7F747967}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId80">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="86" name="Ink 85">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18F1CFB1-BEB6-4081-AE76-8FF56A1B826D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="86" name="Ink 85">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18F1CFB1-BEB6-4081-AE76-8FF56A1B826D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId81">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="87" name="Ink 86">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1FF6B9F-0FA2-4E8D-92AB-F2ADE7801C4B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="87" name="Ink 86">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1FF6B9F-0FA2-4E8D-92AB-F2ADE7801C4B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId82">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="88" name="Ink 87">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FAEFD79-4D2D-4B35-9B22-8062648DA680}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="88" name="Ink 87">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FAEFD79-4D2D-4B35-9B22-8062648DA680}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId83">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="89" name="Ink 88">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05D83CC6-B43D-4529-9AF4-E38CAEB0A969}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="89" name="Ink 88">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05D83CC6-B43D-4529-9AF4-E38CAEB0A969}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId84">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="90" name="Ink 89">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{346BB4A4-3F3F-423B-88C3-05B62150BFC5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="90" name="Ink 89">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{346BB4A4-3F3F-423B-88C3-05B62150BFC5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2295360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18960</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="360" cy="360"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId85">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="91" name="Ink 90">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B2AED50-52E3-4968-9A09-896F894D00AC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2295360" y="18259335"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="91" name="Ink 90">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B2AED50-52E3-4968-9A09-896F894D00AC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2289240" y="18253215"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T14:46:03.331"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'0'0'-8191</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink10.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:24.132"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink11.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:24.133"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink12.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:24.145"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink13.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:24.148"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink14.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:24.149"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink15.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:24.150"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink16.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:30.389"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink17.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:30.390"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink18.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:30.391"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink19.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:30.392"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T14:46:03.833"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">13 1 24575,'-5'0'0,"-2"0"-8191</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink20.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:30.393"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink21.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:30.394"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink22.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:30.404"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink23.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.452"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink24.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.453"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink25.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.454"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink26.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.455"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink27.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.456"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink28.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.457"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink29.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.458"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T14:56:53.425"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'0'0'-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="250.98">1 1 24575,'0'0'-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="486.45">1 1 24575,'0'0'-8191</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="643.93">1 1 24575,'0'0'-8191</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink30.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.459"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink31.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.460"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink32.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.461"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink33.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.462"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink34.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.463"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink35.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.464"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink36.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.465"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink37.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.466"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink38.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.467"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink39.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.468"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink4.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T14:57:02.476"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 49 24575,'0'-5'0,"0"-6"0,0-5 0,0 0-8191</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink40.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.469"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink41.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.470"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink42.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.471"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink43.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.472"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink44.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.473"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink45.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.474"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink46.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.475"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink47.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.476"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink48.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.477"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink49.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.478"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink5.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T14:57:04.737"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'0'0'-8191</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink50.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.479"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink51.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.480"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink52.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.481"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink53.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.482"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink54.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.483"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink55.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.484"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink56.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.485"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink57.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.486"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink58.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.487"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink59.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.488"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink6.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T14:57:05.364"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink60.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.489"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink61.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.490"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink62.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.491"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink63.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.492"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink64.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.493"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink65.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.494"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink66.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.495"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink67.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.496"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink68.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.497"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink69.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.498"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink7.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T14:57:05.913"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575,'55'20'0,"-35"-15"0,-1 1 0,31 13 0,-32-11 0,-1-1 0,1-1 0,23 4 0,-33-8 0,0 1 0,0-1 0,-1 1 0,1 1 0,-1-1 0,7 6 0,35 15 0,-13-14 0,57 9 0,40 7 0,-119-23 34,-1 1-1,0 0 0,23 10 1,25 8-1533,-42-18-5327</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink70.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.499"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink71.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.500"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink72.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.501"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink73.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.502"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink74.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.503"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink75.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.504"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink76.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.505"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink77.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.506"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink78.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.507"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink79.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.508"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink8.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T14:57:45.561"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink80.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.509"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink81.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.510"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink82.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:32.511"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink9.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-25T15:01:24.116"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1 24575</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1080,7 +8333,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ77"/>
+  <dimension ref="A1:AQ71"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
@@ -1100,13 +8353,13 @@
       <c r="E1" s="25"/>
       <c r="F1" s="25"/>
       <c r="G1" s="25" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -1118,14 +8371,14 @@
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="37" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="B3" s="38"/>
       <c r="C3" s="38"/>
       <c r="D3" s="38"/>
       <c r="E3" s="39"/>
       <c r="F3" s="43" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G3" s="38"/>
       <c r="H3" s="44"/>
@@ -1135,25 +8388,25 @@
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="40" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B4" s="41"/>
       <c r="C4" s="41"/>
       <c r="D4" s="41"/>
       <c r="E4" s="42"/>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>29</v>
+      <c r="H4" s="16" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B5" s="35"/>
       <c r="C5" s="35"/>
@@ -1165,50 +8418,50 @@
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="24"/>
       <c r="B7" s="33"/>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="E7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="F7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="G7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="H7" s="18" t="s">
         <v>17</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>18</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1248,7 +8501,7 @@
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="27"/>
       <c r="C8" s="27"/>
@@ -1295,21 +8548,21 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="21" t="s">
-        <v>20</v>
+      <c r="B9" s="6"/>
+      <c r="C9" s="19" t="s">
+        <v>19</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>20</v>
+      <c r="D9" s="19" t="s">
+        <v>19</v>
       </c>
-      <c r="E9" s="21"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="21" t="s">
-        <v>20</v>
+      <c r="E9" s="19"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="19" t="s">
+        <v>19</v>
       </c>
-      <c r="H9" s="15"/>
+      <c r="H9" s="13"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1347,25 +8600,25 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
-        <v>26</v>
+      <c r="A10" s="7" t="s">
+        <v>24</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="14" t="s">
-        <v>20</v>
+      <c r="B10" s="6"/>
+      <c r="C10" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>20</v>
+      <c r="D10" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14" t="s">
-        <v>20</v>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="G10" s="14" t="s">
-        <v>20</v>
+      <c r="G10" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="H10" s="15" t="s">
-        <v>20</v>
+      <c r="H10" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1404,22 +8657,22 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
-        <v>35</v>
+      <c r="A11" s="7" t="s">
+        <v>32</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="14" t="s">
-        <v>20</v>
+      <c r="B11" s="6"/>
+      <c r="C11" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>20</v>
+      <c r="D11" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14" t="s">
-        <v>20</v>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="15"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="13"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1457,19 +8710,19 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
-        <v>36</v>
+      <c r="A12" s="7" t="s">
+        <v>33</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14" t="s">
-        <v>20</v>
+      <c r="B12" s="6"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="G12" s="14"/>
-      <c r="H12" s="15" t="s">
-        <v>20</v>
+      <c r="G12" s="12"/>
+      <c r="H12" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1508,21 +8761,21 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
-        <v>25</v>
+      <c r="A13" s="7" t="s">
+        <v>23</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14" t="s">
-        <v>20</v>
+      <c r="B13" s="6"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="G13" s="14" t="s">
-        <v>20</v>
+      <c r="G13" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="H13" s="15" t="s">
-        <v>20</v>
+      <c r="H13" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1561,20 +8814,16 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
-        <v>37</v>
+      <c r="A14" s="7" t="s">
+        <v>51</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="15"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="13"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1611,17 +8860,17 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A15" s="29" t="s">
-        <v>21</v>
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
+        <v>50</v>
       </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="31"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="13"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1659,24 +8908,20 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
-        <v>32</v>
+      <c r="A16" s="7" t="s">
+        <v>34</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>33</v>
+      <c r="B16" s="6"/>
+      <c r="C16" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14" t="s">
-        <v>20</v>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="E16" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="15"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="13"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1713,15 +8958,17 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="9"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="15"/>
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A17" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="31"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1759,14 +9006,24 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="9"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
+      <c r="A18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="13"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1803,15 +9060,17 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="15"/>
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A19" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="31"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1849,14 +9108,28 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="9"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="15"/>
+      <c r="A20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>19</v>
+      </c>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1894,14 +9167,28 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="9"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="15"/>
+      <c r="A21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>19</v>
+      </c>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -1938,15 +9225,17 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="9"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="15"/>
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -1974,26 +9263,26 @@
       <c r="AG22"/>
       <c r="AH22"/>
       <c r="AI22"/>
-      <c r="AJ22"/>
-      <c r="AK22"/>
-      <c r="AL22"/>
-      <c r="AM22"/>
-      <c r="AN22"/>
-      <c r="AO22"/>
-      <c r="AP22"/>
-      <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A23" s="29" t="s">
-        <v>22</v>
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>39</v>
       </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="31"/>
+      <c r="B23" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="14"/>
+      <c r="H23" s="15"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2030,27 +9319,19 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
-        <v>31</v>
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
-      <c r="C24" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>20</v>
-      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2087,25 +9368,21 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="9"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="14" t="s">
-        <v>20</v>
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>52</v>
       </c>
-      <c r="D25" s="14" t="s">
-        <v>20</v>
+      <c r="B25" s="22" t="s">
+        <v>45</v>
       </c>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14" t="s">
-        <v>20</v>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8" t="s">
+        <v>42</v>
       </c>
-      <c r="G25" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>20</v>
-      </c>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2142,276 +9419,65 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="9"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="15"/>
-      <c r="I26"/>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26"/>
-      <c r="M26"/>
-      <c r="N26"/>
-      <c r="O26"/>
-      <c r="P26"/>
-      <c r="Q26"/>
-      <c r="R26"/>
-      <c r="S26"/>
-      <c r="T26"/>
-      <c r="U26"/>
-      <c r="V26"/>
-      <c r="W26"/>
-      <c r="X26"/>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AA26"/>
-      <c r="AB26"/>
-      <c r="AC26"/>
-      <c r="AD26"/>
-      <c r="AE26"/>
-      <c r="AF26"/>
-      <c r="AG26"/>
-      <c r="AH26"/>
-      <c r="AI26"/>
-      <c r="AJ26"/>
-      <c r="AK26"/>
-      <c r="AL26"/>
-      <c r="AM26"/>
-      <c r="AN26"/>
-      <c r="AO26"/>
-      <c r="AP26"/>
-      <c r="AQ26"/>
+    <row r="26" spans="1:43" customFormat="1" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="9"/>
+    <row r="27" spans="1:43" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="B27" s="8"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="15"/>
-      <c r="I27"/>
-      <c r="J27"/>
-      <c r="K27"/>
-      <c r="L27"/>
-      <c r="M27"/>
-      <c r="N27"/>
-      <c r="O27"/>
-      <c r="P27"/>
-      <c r="Q27"/>
-      <c r="R27"/>
-      <c r="S27"/>
-      <c r="T27"/>
-      <c r="U27"/>
-      <c r="V27"/>
-      <c r="W27"/>
-      <c r="X27"/>
-      <c r="Y27"/>
-      <c r="Z27"/>
-      <c r="AA27"/>
-      <c r="AB27"/>
-      <c r="AC27"/>
-      <c r="AD27"/>
-      <c r="AE27"/>
-      <c r="AF27"/>
-      <c r="AG27"/>
-      <c r="AH27"/>
-      <c r="AI27"/>
-      <c r="AJ27"/>
-      <c r="AK27"/>
-      <c r="AL27"/>
-      <c r="AM27"/>
-      <c r="AN27"/>
-      <c r="AO27"/>
-      <c r="AP27"/>
-      <c r="AQ27"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="9"/>
+    <row r="28" spans="1:43" customFormat="1" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8"/>
       <c r="B28" s="8"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="15"/>
-      <c r="I28"/>
-      <c r="J28"/>
-      <c r="K28"/>
-      <c r="L28"/>
-      <c r="M28"/>
-      <c r="N28"/>
-      <c r="O28"/>
-      <c r="P28"/>
-      <c r="Q28"/>
-      <c r="R28"/>
-      <c r="S28"/>
-      <c r="T28"/>
-      <c r="U28"/>
-      <c r="V28"/>
-      <c r="W28"/>
-      <c r="X28"/>
-      <c r="Y28"/>
-      <c r="Z28"/>
-      <c r="AA28"/>
-      <c r="AB28"/>
-      <c r="AC28"/>
-      <c r="AD28"/>
-      <c r="AE28"/>
-      <c r="AF28"/>
-      <c r="AG28"/>
-      <c r="AH28"/>
-      <c r="AI28"/>
-      <c r="AJ28"/>
-      <c r="AK28"/>
-      <c r="AL28"/>
-      <c r="AM28"/>
-      <c r="AN28"/>
-      <c r="AO28"/>
-      <c r="AP28"/>
-      <c r="AQ28"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="9"/>
+    <row r="29" spans="1:43" customFormat="1" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="8"/>
       <c r="B29" s="8"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="15"/>
-      <c r="I29"/>
-      <c r="J29"/>
-      <c r="K29"/>
-      <c r="L29"/>
-      <c r="M29"/>
-      <c r="N29"/>
-      <c r="O29"/>
-      <c r="P29"/>
-      <c r="Q29"/>
-      <c r="R29"/>
-      <c r="S29"/>
-      <c r="T29"/>
-      <c r="U29"/>
-      <c r="V29"/>
-      <c r="W29"/>
-      <c r="X29"/>
-      <c r="Y29"/>
-      <c r="Z29"/>
-      <c r="AA29"/>
-      <c r="AB29"/>
-      <c r="AC29"/>
-      <c r="AD29"/>
-      <c r="AE29"/>
-      <c r="AF29"/>
-      <c r="AG29"/>
-      <c r="AH29"/>
-      <c r="AI29"/>
-      <c r="AJ29"/>
-      <c r="AK29"/>
-      <c r="AL29"/>
-      <c r="AM29"/>
-      <c r="AN29"/>
-      <c r="AO29"/>
-      <c r="AP29"/>
-      <c r="AQ29"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="17"/>
-      <c r="I30"/>
-      <c r="J30"/>
-      <c r="K30"/>
-      <c r="L30"/>
-      <c r="M30"/>
-      <c r="N30"/>
-      <c r="O30"/>
-      <c r="P30"/>
-      <c r="Q30"/>
-      <c r="R30"/>
-      <c r="S30"/>
-      <c r="T30"/>
-      <c r="U30"/>
-      <c r="V30"/>
-      <c r="W30"/>
-      <c r="X30"/>
-      <c r="Y30"/>
-      <c r="Z30"/>
-      <c r="AA30"/>
-      <c r="AB30"/>
-      <c r="AC30"/>
-      <c r="AD30"/>
-      <c r="AE30"/>
-      <c r="AF30"/>
-      <c r="AG30"/>
-      <c r="AH30"/>
-      <c r="AI30"/>
-      <c r="AJ30"/>
-      <c r="AK30"/>
-      <c r="AL30"/>
-      <c r="AM30"/>
-      <c r="AN30"/>
-      <c r="AO30"/>
-      <c r="AP30"/>
-      <c r="AQ30"/>
+    <row r="30" spans="1:43" customFormat="1" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A31" s="5"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31"/>
-      <c r="J31"/>
-      <c r="K31"/>
-      <c r="L31"/>
-      <c r="M31"/>
-      <c r="N31"/>
-      <c r="O31"/>
-      <c r="P31"/>
-      <c r="Q31"/>
-      <c r="R31"/>
-      <c r="S31"/>
-      <c r="T31"/>
-      <c r="U31"/>
-      <c r="V31"/>
-      <c r="W31"/>
-      <c r="X31"/>
-      <c r="Y31"/>
-      <c r="Z31"/>
-      <c r="AA31"/>
-      <c r="AB31"/>
-      <c r="AC31"/>
-      <c r="AD31"/>
-      <c r="AE31"/>
-      <c r="AF31"/>
-      <c r="AG31"/>
-      <c r="AH31"/>
-      <c r="AI31"/>
-      <c r="AJ31"/>
-      <c r="AK31"/>
-      <c r="AL31"/>
-      <c r="AM31"/>
-      <c r="AN31"/>
-      <c r="AO31"/>
-      <c r="AP31"/>
-      <c r="AQ31"/>
-    </row>
+    <row r="31" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="32" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="33" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="34" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -2445,19 +9511,22 @@
     <row r="62" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="63" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="64" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="66" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="69" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="71" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="G1:H1"/>
@@ -2468,8 +9537,8 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
   </mergeCells>
@@ -2478,6 +9547,7 @@
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
